--- a/observations/calibrations/solar_calibrations.xlsx
+++ b/observations/calibrations/solar_calibrations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iant\Documents\PROGRAMS\nomad_obs\observations\calibrations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C00FA75-1BC2-4A80-8A2C-7EAACA457B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1109F2-6364-4C22-8458-7288EC91C1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -919,7 +919,7 @@
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1056,6 +1056,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1068,8 +1069,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
@@ -1392,23 +1391,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE150"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.28515625" customWidth="1"/>
-    <col min="23" max="23" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.33203125" customWidth="1"/>
+    <col min="23" max="23" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1416,12 +1415,12 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="2:31" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:31" ht="18" x14ac:dyDescent="0.35">
       <c r="W2" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="2:31" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:31" ht="18" x14ac:dyDescent="0.35">
       <c r="B3" s="14" t="s">
         <v>3</v>
       </c>
@@ -1434,7 +1433,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:31" x14ac:dyDescent="0.3">
       <c r="C4" s="13" t="s">
         <v>12</v>
       </c>
@@ -1473,7 +1472,7 @@
       <c r="AD4" s="71"/>
       <c r="AE4" s="65"/>
     </row>
-    <row r="5" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:31" x14ac:dyDescent="0.3">
       <c r="C5" s="19" t="s">
         <v>1</v>
       </c>
@@ -1518,7 +1517,7 @@
       </c>
       <c r="AE5" s="4"/>
     </row>
-    <row r="6" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:31" x14ac:dyDescent="0.3">
       <c r="C6" s="20" t="s">
         <v>2</v>
       </c>
@@ -1583,14 +1582,14 @@
       <c r="AD6" s="7"/>
       <c r="AE6" s="8"/>
     </row>
-    <row r="9" spans="2:31" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:31" ht="18" x14ac:dyDescent="0.35">
       <c r="B9" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:31" x14ac:dyDescent="0.3">
       <c r="C10" s="13" t="s">
         <v>12</v>
       </c>
@@ -1600,13 +1599,13 @@
       <c r="E10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="100" t="s">
+      <c r="F10" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="101"/>
-      <c r="H10" s="101"/>
-      <c r="I10" s="101"/>
-      <c r="J10" s="101"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="102"/>
       <c r="K10" s="71"/>
       <c r="L10" s="71"/>
       <c r="M10" s="71"/>
@@ -1631,7 +1630,7 @@
       <c r="AD10" s="71"/>
       <c r="AE10" s="65"/>
     </row>
-    <row r="11" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:31" x14ac:dyDescent="0.3">
       <c r="C11" s="19" t="s">
         <v>34</v>
       </c>
@@ -1692,7 +1691,7 @@
       <c r="AD11" s="16"/>
       <c r="AE11" s="17"/>
     </row>
-    <row r="12" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:31" x14ac:dyDescent="0.3">
       <c r="C12" s="20" t="s">
         <v>36</v>
       </c>
@@ -1737,12 +1736,12 @@
       <c r="AD12" s="7"/>
       <c r="AE12" s="8"/>
     </row>
-    <row r="13" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:31" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="2:31" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:31" ht="18" x14ac:dyDescent="0.35">
       <c r="B15" s="14" t="s">
         <v>0</v>
       </c>
@@ -1756,40 +1755,40 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:31" x14ac:dyDescent="0.3">
       <c r="AC16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B17" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="102" t="s">
+      <c r="F17" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="103"/>
-      <c r="J17" s="103"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="104"/>
       <c r="L17" s="9" t="s">
         <v>2</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="9"/>
       <c r="O17" s="9"/>
-      <c r="P17" s="102" t="s">
+      <c r="P17" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="Q17" s="103"/>
-      <c r="R17" s="103"/>
-      <c r="S17" s="103"/>
-      <c r="T17" s="103"/>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="Q17" s="104"/>
+      <c r="R17" s="104"/>
+      <c r="S17" s="104"/>
+      <c r="T17" s="104"/>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B18" s="39" t="s">
         <v>10</v>
       </c>
@@ -1864,7 +1863,7 @@
       </c>
       <c r="AE18" s="9"/>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -1919,7 +1918,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1</v>
       </c>
@@ -1968,7 +1967,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1</v>
       </c>
@@ -2015,7 +2014,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1</v>
       </c>
@@ -2079,7 +2078,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1</v>
       </c>
@@ -2128,7 +2127,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1</v>
       </c>
@@ -2177,7 +2176,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1</v>
       </c>
@@ -2237,7 +2236,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
@@ -2286,7 +2285,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1</v>
       </c>
@@ -2338,7 +2337,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1</v>
       </c>
@@ -2383,7 +2382,7 @@
       </c>
       <c r="Z28" s="55"/>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1</v>
       </c>
@@ -2426,7 +2425,7 @@
       <c r="Y29" s="48"/>
       <c r="Z29" s="49"/>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1</v>
       </c>
@@ -2475,7 +2474,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1</v>
       </c>
@@ -2520,7 +2519,7 @@
       <c r="Y31" s="48"/>
       <c r="Z31" s="49"/>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1</v>
       </c>
@@ -2572,7 +2571,7 @@
       <c r="Y32" s="48"/>
       <c r="Z32" s="49"/>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1</v>
       </c>
@@ -2617,7 +2616,7 @@
       <c r="Y33" s="48"/>
       <c r="Z33" s="49"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1</v>
       </c>
@@ -2669,7 +2668,7 @@
       <c r="Y34" s="48"/>
       <c r="Z34" s="49"/>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1</v>
       </c>
@@ -2715,7 +2714,7 @@
       <c r="Y35" s="48"/>
       <c r="Z35" s="49"/>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1</v>
       </c>
@@ -2760,7 +2759,7 @@
       <c r="Y36" s="48"/>
       <c r="Z36" s="49"/>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1</v>
       </c>
@@ -2803,7 +2802,7 @@
       <c r="Y37" s="48"/>
       <c r="Z37" s="49"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1</v>
       </c>
@@ -2846,7 +2845,7 @@
       <c r="Y38" s="48"/>
       <c r="Z38" s="49"/>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1</v>
       </c>
@@ -2892,7 +2891,7 @@
       <c r="Y39" s="48"/>
       <c r="Z39" s="49"/>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1</v>
       </c>
@@ -2935,7 +2934,7 @@
       <c r="Y40" s="48"/>
       <c r="Z40" s="49"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1</v>
       </c>
@@ -2985,7 +2984,7 @@
       <c r="Y41" s="48"/>
       <c r="Z41" s="49"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1</v>
       </c>
@@ -3036,7 +3035,7 @@
       <c r="Y42" s="48"/>
       <c r="Z42" s="49"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1</v>
       </c>
@@ -3091,7 +3090,7 @@
       <c r="Y43" s="48"/>
       <c r="Z43" s="49"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1</v>
       </c>
@@ -3138,7 +3137,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1</v>
       </c>
@@ -3157,7 +3156,9 @@
       <c r="F45" s="81">
         <v>65</v>
       </c>
-      <c r="G45" s="73"/>
+      <c r="G45" s="79">
+        <v>112</v>
+      </c>
       <c r="H45" s="73"/>
       <c r="I45" s="73"/>
       <c r="J45" s="85"/>
@@ -3184,7 +3185,7 @@
       <c r="Y45" s="5"/>
       <c r="Z45" s="4"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1</v>
       </c>
@@ -3200,7 +3201,9 @@
       <c r="E46">
         <v>81</v>
       </c>
-      <c r="F46" s="5"/>
+      <c r="F46" s="2">
+        <v>112</v>
+      </c>
       <c r="J46" s="4"/>
       <c r="L46" s="25">
         <v>199</v>
@@ -3225,7 +3228,7 @@
       <c r="Y46" s="5"/>
       <c r="Z46" s="4"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1</v>
       </c>
@@ -3246,6 +3249,9 @@
       </c>
       <c r="G47" s="3">
         <v>103</v>
+      </c>
+      <c r="H47" s="3">
+        <v>112</v>
       </c>
       <c r="J47" s="4"/>
       <c r="L47" s="25">
@@ -3269,7 +3275,7 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="4"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1</v>
       </c>
@@ -3291,7 +3297,9 @@
       <c r="G48" s="18">
         <v>103</v>
       </c>
-      <c r="H48" s="7"/>
+      <c r="H48" s="18">
+        <v>112</v>
+      </c>
       <c r="I48" s="7"/>
       <c r="J48" s="8"/>
       <c r="L48" s="34">
@@ -3320,7 +3328,7 @@
       <c r="Y48" s="5"/>
       <c r="Z48" s="4"/>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
       <c r="W49" s="5">
         <v>4526.9799999999996</v>
       </c>
@@ -3330,7 +3338,7 @@
       <c r="Y49" s="6"/>
       <c r="Z49" s="8"/>
     </row>
-    <row r="50" spans="1:26" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:26" ht="18" x14ac:dyDescent="0.35">
       <c r="B50" s="14" t="s">
         <v>0</v>
       </c>
@@ -3342,7 +3350,7 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -3353,35 +3361,35 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B52" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C52" s="13"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
-      <c r="F52" s="102" t="s">
+      <c r="F52" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="G52" s="103"/>
-      <c r="H52" s="103"/>
-      <c r="I52" s="103"/>
-      <c r="J52" s="103"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="104"/>
       <c r="L52" s="9" t="s">
         <v>2</v>
       </c>
       <c r="M52" s="13"/>
       <c r="N52" s="9"/>
       <c r="O52" s="9"/>
-      <c r="P52" s="102" t="s">
+      <c r="P52" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="Q52" s="103"/>
-      <c r="R52" s="103"/>
-      <c r="S52" s="103"/>
-      <c r="T52" s="103"/>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Q52" s="104"/>
+      <c r="R52" s="104"/>
+      <c r="S52" s="104"/>
+      <c r="T52" s="104"/>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B53" s="9" t="s">
         <v>10</v>
       </c>
@@ -3437,7 +3445,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>2</v>
       </c>
@@ -3474,7 +3482,7 @@
       </c>
       <c r="T54" s="4"/>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2</v>
       </c>
@@ -3511,7 +3519,7 @@
       <c r="P55" s="5"/>
       <c r="T55" s="4"/>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2</v>
       </c>
@@ -3563,7 +3571,7 @@
       <c r="S56" s="30"/>
       <c r="T56" s="31"/>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>2</v>
       </c>
@@ -3600,7 +3608,7 @@
       <c r="P57" s="5"/>
       <c r="T57" s="4"/>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>2</v>
       </c>
@@ -3637,7 +3645,7 @@
       <c r="P58" s="5"/>
       <c r="T58" s="4"/>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>2</v>
       </c>
@@ -3678,7 +3686,7 @@
       </c>
       <c r="T59" s="4"/>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2</v>
       </c>
@@ -3715,7 +3723,7 @@
       <c r="P60" s="5"/>
       <c r="T60" s="4"/>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2</v>
       </c>
@@ -3767,7 +3775,7 @@
       <c r="S61" s="30"/>
       <c r="T61" s="31"/>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2</v>
       </c>
@@ -3804,7 +3812,7 @@
       <c r="P62" s="5"/>
       <c r="T62" s="4"/>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2</v>
       </c>
@@ -3856,7 +3864,7 @@
       <c r="S63" s="30"/>
       <c r="T63" s="31"/>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2</v>
       </c>
@@ -3893,7 +3901,7 @@
       <c r="P64" s="5"/>
       <c r="T64" s="4"/>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2</v>
       </c>
@@ -3930,7 +3938,7 @@
       <c r="P65" s="35"/>
       <c r="T65" s="4"/>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2</v>
       </c>
@@ -3967,7 +3975,7 @@
       <c r="P66" s="5"/>
       <c r="T66" s="4"/>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2</v>
       </c>
@@ -4004,7 +4012,7 @@
       <c r="P67" s="5"/>
       <c r="T67" s="4"/>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>2</v>
       </c>
@@ -4056,7 +4064,7 @@
       <c r="S68" s="30"/>
       <c r="T68" s="31"/>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2</v>
       </c>
@@ -4103,7 +4111,7 @@
       </c>
       <c r="T69" s="4"/>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>2</v>
       </c>
@@ -4144,7 +4152,7 @@
       </c>
       <c r="T70" s="4"/>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>2</v>
       </c>
@@ -4181,7 +4189,7 @@
       <c r="P71" s="5"/>
       <c r="T71" s="4"/>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>2</v>
       </c>
@@ -4218,7 +4226,7 @@
       <c r="P72" s="5"/>
       <c r="T72" s="4"/>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>2</v>
       </c>
@@ -4255,7 +4263,7 @@
       <c r="P73" s="5"/>
       <c r="T73" s="4"/>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>2</v>
       </c>
@@ -4292,7 +4300,7 @@
       <c r="P74" s="5"/>
       <c r="T74" s="4"/>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>2</v>
       </c>
@@ -4329,7 +4337,7 @@
       <c r="P75" s="5"/>
       <c r="T75" s="4"/>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>2</v>
       </c>
@@ -4370,7 +4378,7 @@
       </c>
       <c r="T76" s="4"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>2</v>
       </c>
@@ -4414,7 +4422,7 @@
       </c>
       <c r="T77" s="4"/>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>2</v>
       </c>
@@ -4451,7 +4459,7 @@
       <c r="P78" s="5"/>
       <c r="T78" s="4"/>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>2</v>
       </c>
@@ -4499,7 +4507,7 @@
       <c r="S79" s="30"/>
       <c r="T79" s="31"/>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>2</v>
       </c>
@@ -4536,7 +4544,7 @@
       <c r="P80" s="5"/>
       <c r="T80" s="4"/>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>2</v>
       </c>
@@ -4573,7 +4581,7 @@
       <c r="P81" s="5"/>
       <c r="T81" s="4"/>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>2</v>
       </c>
@@ -4616,7 +4624,7 @@
       <c r="S82" s="7"/>
       <c r="T82" s="8"/>
     </row>
-    <row r="84" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="B84" s="14" t="s">
         <v>0</v>
       </c>
@@ -4630,7 +4638,7 @@
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -4638,35 +4646,35 @@
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B86" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C86" s="13"/>
       <c r="D86" s="9"/>
       <c r="E86" s="33"/>
-      <c r="F86" s="102" t="s">
+      <c r="F86" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="G86" s="103"/>
-      <c r="H86" s="103"/>
-      <c r="I86" s="103"/>
-      <c r="J86" s="103"/>
+      <c r="G86" s="104"/>
+      <c r="H86" s="104"/>
+      <c r="I86" s="104"/>
+      <c r="J86" s="104"/>
       <c r="L86" s="9" t="s">
         <v>2</v>
       </c>
       <c r="M86" s="13"/>
       <c r="N86" s="9"/>
       <c r="O86" s="33"/>
-      <c r="P86" s="102" t="s">
+      <c r="P86" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="Q86" s="103"/>
-      <c r="R86" s="103"/>
-      <c r="S86" s="103"/>
-      <c r="T86" s="103"/>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q86" s="104"/>
+      <c r="R86" s="104"/>
+      <c r="S86" s="104"/>
+      <c r="T86" s="104"/>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B87" s="9" t="s">
         <v>10</v>
       </c>
@@ -4722,7 +4730,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>4</v>
       </c>
@@ -4763,7 +4771,7 @@
       <c r="S88" s="16"/>
       <c r="T88" s="17"/>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>4</v>
       </c>
@@ -4807,7 +4815,7 @@
       </c>
       <c r="T89" s="4"/>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>4</v>
       </c>
@@ -4859,7 +4867,7 @@
       <c r="S90" s="30"/>
       <c r="T90" s="31"/>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>4</v>
       </c>
@@ -4907,7 +4915,7 @@
       </c>
       <c r="T91" s="4"/>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>4</v>
       </c>
@@ -4946,7 +4954,7 @@
       <c r="P92" s="5"/>
       <c r="T92" s="4"/>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>4</v>
       </c>
@@ -4985,7 +4993,7 @@
       <c r="P93" s="5"/>
       <c r="T93" s="4"/>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>4</v>
       </c>
@@ -5029,7 +5037,7 @@
       </c>
       <c r="T94" s="4"/>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>4</v>
       </c>
@@ -5083,7 +5091,7 @@
       <c r="S95" s="30"/>
       <c r="T95" s="31"/>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>4</v>
       </c>
@@ -5124,7 +5132,7 @@
       </c>
       <c r="T96" s="4"/>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>4</v>
       </c>
@@ -5176,7 +5184,7 @@
       <c r="S97" s="30"/>
       <c r="T97" s="31"/>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>4</v>
       </c>
@@ -5225,7 +5233,7 @@
       <c r="S98" s="30"/>
       <c r="T98" s="31"/>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>4</v>
       </c>
@@ -5266,7 +5274,7 @@
       </c>
       <c r="T99" s="4"/>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>4</v>
       </c>
@@ -5307,7 +5315,7 @@
       </c>
       <c r="T100" s="4"/>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>4</v>
       </c>
@@ -5348,7 +5356,7 @@
       </c>
       <c r="T101" s="4"/>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>4</v>
       </c>
@@ -5400,7 +5408,7 @@
       <c r="S102" s="30"/>
       <c r="T102" s="31"/>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>4</v>
       </c>
@@ -5449,7 +5457,7 @@
       </c>
       <c r="T103" s="4"/>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>4</v>
       </c>
@@ -5495,7 +5503,7 @@
       </c>
       <c r="T104" s="4"/>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>4</v>
       </c>
@@ -5539,7 +5547,7 @@
       </c>
       <c r="T105" s="4"/>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>4</v>
       </c>
@@ -5583,7 +5591,7 @@
       </c>
       <c r="T106" s="4"/>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>4</v>
       </c>
@@ -5627,7 +5635,7 @@
       </c>
       <c r="T107" s="4"/>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>4</v>
       </c>
@@ -5671,7 +5679,7 @@
       </c>
       <c r="T108" s="4"/>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>4</v>
       </c>
@@ -5715,7 +5723,7 @@
       </c>
       <c r="T109" s="4"/>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>4</v>
       </c>
@@ -5759,7 +5767,7 @@
       </c>
       <c r="T110" s="4"/>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>4</v>
       </c>
@@ -5812,7 +5820,7 @@
       </c>
       <c r="T111" s="4"/>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>4</v>
       </c>
@@ -5865,7 +5873,7 @@
       </c>
       <c r="T112" s="4"/>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>4</v>
       </c>
@@ -5919,7 +5927,7 @@
       <c r="S113" s="30"/>
       <c r="T113" s="31"/>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>4</v>
       </c>
@@ -5970,7 +5978,7 @@
       <c r="Q114" s="73"/>
       <c r="T114" s="4"/>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>4</v>
       </c>
@@ -6015,7 +6023,7 @@
       <c r="P115" s="5"/>
       <c r="T115" s="4"/>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>4</v>
       </c>
@@ -6063,7 +6071,7 @@
       <c r="S116" s="7"/>
       <c r="T116" s="8"/>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>4</v>
       </c>
@@ -6085,14 +6093,14 @@
       <c r="H117" s="3">
         <v>109</v>
       </c>
-      <c r="I117" s="104">
+      <c r="I117" s="3">
         <v>111</v>
       </c>
       <c r="J117" s="4"/>
       <c r="M117" s="89"/>
       <c r="N117" s="90"/>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>4</v>
       </c>
@@ -6117,19 +6125,19 @@
       <c r="I118" s="18">
         <v>109</v>
       </c>
-      <c r="J118" s="105">
+      <c r="J118" s="100">
         <v>111</v>
       </c>
       <c r="M118" s="89"/>
       <c r="N118" s="90"/>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C119" s="89"/>
       <c r="D119" s="90"/>
       <c r="M119" s="89"/>
       <c r="N119" s="90"/>
     </row>
-    <row r="121" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="B121" s="14" t="s">
         <v>0</v>
       </c>
@@ -6141,7 +6149,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
@@ -6149,34 +6157,34 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B123" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C123" s="40"/>
       <c r="D123" s="9"/>
-      <c r="F123" s="102" t="s">
+      <c r="F123" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="G123" s="103"/>
-      <c r="H123" s="103"/>
-      <c r="I123" s="103"/>
-      <c r="J123" s="103"/>
+      <c r="G123" s="104"/>
+      <c r="H123" s="104"/>
+      <c r="I123" s="104"/>
+      <c r="J123" s="104"/>
       <c r="L123" s="9" t="s">
         <v>2</v>
       </c>
       <c r="M123" s="40"/>
       <c r="N123" s="9"/>
       <c r="O123" s="33"/>
-      <c r="P123" s="102" t="s">
+      <c r="P123" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="Q123" s="103"/>
-      <c r="R123" s="103"/>
-      <c r="S123" s="103"/>
-      <c r="T123" s="103"/>
-    </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q123" s="104"/>
+      <c r="R123" s="104"/>
+      <c r="S123" s="104"/>
+      <c r="T123" s="104"/>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B124" s="9" t="s">
         <v>10</v>
       </c>
@@ -6232,7 +6240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>8</v>
       </c>
@@ -6271,7 +6279,7 @@
       <c r="S125" s="30"/>
       <c r="T125" s="31"/>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>8</v>
       </c>
@@ -6308,7 +6316,7 @@
       </c>
       <c r="T126" s="4"/>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>8</v>
       </c>
@@ -6361,7 +6369,7 @@
       <c r="S127" s="30"/>
       <c r="T127" s="31"/>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>8</v>
       </c>
@@ -6413,7 +6421,7 @@
       </c>
       <c r="T128" s="4"/>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>8</v>
       </c>
@@ -6465,7 +6473,7 @@
       </c>
       <c r="T129" s="4"/>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>8</v>
       </c>
@@ -6519,7 +6527,7 @@
       <c r="S130" s="30"/>
       <c r="T130" s="31"/>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>8</v>
       </c>
@@ -6572,7 +6580,7 @@
       <c r="S131" s="30"/>
       <c r="T131" s="31"/>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>8</v>
       </c>
@@ -6626,7 +6634,7 @@
       <c r="S132" s="30"/>
       <c r="T132" s="31"/>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>8</v>
       </c>
@@ -6677,7 +6685,7 @@
       <c r="S133" s="30"/>
       <c r="T133" s="31"/>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>8</v>
       </c>
@@ -6729,7 +6737,7 @@
       </c>
       <c r="T134" s="4"/>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>8</v>
       </c>
@@ -6781,7 +6789,7 @@
       </c>
       <c r="T135" s="4"/>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>8</v>
       </c>
@@ -6833,7 +6841,7 @@
       </c>
       <c r="T136" s="4"/>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>8</v>
       </c>
@@ -6886,7 +6894,7 @@
       </c>
       <c r="T137" s="4"/>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>8</v>
       </c>
@@ -6940,7 +6948,7 @@
       </c>
       <c r="T138" s="4"/>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>8</v>
       </c>
@@ -6995,7 +7003,7 @@
       <c r="S139" s="30"/>
       <c r="T139" s="31"/>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>8</v>
       </c>
@@ -7036,7 +7044,7 @@
       <c r="P140" s="5"/>
       <c r="T140" s="4"/>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>8</v>
       </c>
@@ -7081,7 +7089,7 @@
       <c r="S141" s="7"/>
       <c r="T141" s="8"/>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>40</v>
       </c>
@@ -7101,7 +7109,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="145" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>41</v>
       </c>
@@ -7109,7 +7117,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="146" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B146">
         <v>125</v>
       </c>
@@ -7117,7 +7125,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="147" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B147">
         <v>126</v>
       </c>
@@ -7125,7 +7133,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="149" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>42</v>
       </c>
@@ -7133,7 +7141,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="150" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B150" t="str">
         <f ca="1">"3,1,"&amp;INDIRECT(D144&amp;B146)&amp;","&amp;INDIRECT(D144&amp;B147)&amp;",0,-1,NONE,NONE,SO MINISCAN "&amp;A141&amp;"KHZ STARTING ORDER "&amp;INDIRECT(C144&amp;B146)&amp;" &amp; "&amp;INDIRECT(C144&amp;B147)</f>
         <v>3,1,220,221,0,-1,NONE,NONE,SO MINISCAN 8KHZ STARTING ORDER 110 &amp; 116</v>
